--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129332127</v>
+        <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89111</v>
+        <v>89291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,21 +1047,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>809</v>
+        <v>805</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Praktvaxing</t>
+          <t>Scharlakansvaxing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hygrocybe splendidissima</t>
+          <t>Hygrocybe punicea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.D.Orton) M.M.Moser</t>
+          <t>(Fr.) P.Kumm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1071,13 +1071,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>494175</v>
+        <v>494161</v>
       </c>
       <c r="R5" t="n">
-        <v>6416893</v>
+        <v>6416921</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,26 +1101,20 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Till DNA GABFJO 25_08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,13 +1132,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129332127</t>
+          <t>https://artportalen.se/Sighting/137123861</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129332129</v>
+        <v>129332127</v>
       </c>
       <c r="B6" t="n">
         <v>89111</v>
@@ -1179,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>494145</v>
+        <v>494175</v>
       </c>
       <c r="R6" t="n">
-        <v>6416955</v>
+        <v>6416893</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,12 +1211,18 @@
           <t>2025-10-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Till DNA GABFJO 25_08</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1240,13 +1240,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129332129</t>
+          <t>https://artportalen.se/Sighting/129332127</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129332130</v>
+        <v>129332129</v>
       </c>
       <c r="B7" t="n">
         <v>89111</v>
@@ -1281,10 +1281,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>494157</v>
+        <v>494145</v>
       </c>
       <c r="R7" t="n">
-        <v>6416907</v>
+        <v>6416955</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1342,54 +1342,51 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129332130</t>
+          <t>https://artportalen.se/Sighting/129332129</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119302794</v>
+        <v>129332130</v>
       </c>
       <c r="B8" t="n">
-        <v>92564</v>
+        <v>89111</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1339</v>
+        <v>809</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Hygrocybe splendidissima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(P.D.Orton) M.M.Moser</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ulstorp, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>494112</v>
+        <v>494157</v>
       </c>
       <c r="R8" t="n">
-        <v>6417036</v>
+        <v>6416907</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1416,12 +1413,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-23</t>
+          <t>2025-10-25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1430,24 +1427,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1463,38 +1444,38 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119302794</t>
+          <t>https://artportalen.se/Sighting/129332130</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129332145</v>
+        <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>88980</v>
+        <v>89298</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3295</v>
+        <v>809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
+          <t>Hygrocybe splendidissima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.) Corner</t>
+          <t>(P.D.Orton) M.M.Moser</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,13 +1485,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>494147</v>
+        <v>494176</v>
       </c>
       <c r="R9" t="n">
-        <v>6416940</v>
+        <v>6416893</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,12 +1515,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1565,38 +1546,38 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129332145</t>
+          <t>https://artportalen.se/Sighting/137123857</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129332146</v>
+        <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>88980</v>
+        <v>89298</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3295</v>
+        <v>809</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Hagfingersvamp</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Clavulinopsis helvola</t>
+          <t>Hygrocybe splendidissima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pers.) Corner</t>
+          <t>(P.D.Orton) M.M.Moser</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,13 +1587,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>494182</v>
+        <v>494171</v>
       </c>
       <c r="R10" t="n">
-        <v>6416891</v>
+        <v>6416899</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1636,12 +1617,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1667,38 +1648,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129332146</t>
+          <t>https://artportalen.se/Sighting/137123859</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129332155</v>
+        <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>88982</v>
+        <v>89298</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>3297</v>
+        <v>809</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aprikosfingersvamp</t>
+          <t>Praktvaxing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Clavulinopsis luteoalba</t>
+          <t>Hygrocybe splendidissima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Rea) Corner</t>
+          <t>(P.D.Orton) M.M.Moser</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1708,13 +1689,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>494182</v>
+        <v>494145</v>
       </c>
       <c r="R11" t="n">
-        <v>6416891</v>
+        <v>6416933</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1738,12 +1719,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-10-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1769,16 +1750,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129332155</t>
+          <t>https://artportalen.se/Sighting/137123864</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119302852</v>
+        <v>119302794</v>
       </c>
       <c r="B12" t="n">
-        <v>92632</v>
+        <v>92564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1786,21 +1767,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>1339</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,7 +1794,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>494131</v>
+        <v>494112</v>
       </c>
       <c r="R12" t="n">
         <v>6417036</v>
@@ -1890,16 +1871,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119302852</t>
+          <t>https://artportalen.se/Sighting/119302794</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129332153</v>
+        <v>129332145</v>
       </c>
       <c r="B13" t="n">
-        <v>89083</v>
+        <v>88980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,21 +1888,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4377</v>
+        <v>3295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blodvaxing</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hygrocybe coccinea</t>
+          <t>Clavulinopsis helvola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1931,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>494177</v>
+        <v>494147</v>
       </c>
       <c r="R13" t="n">
-        <v>6416891</v>
+        <v>6416940</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1992,16 +1973,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129332153</t>
+          <t>https://artportalen.se/Sighting/129332145</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129332117</v>
+        <v>129332146</v>
       </c>
       <c r="B14" t="n">
-        <v>89035</v>
+        <v>88980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,19 +1990,23 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4398</v>
+        <v>3295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitvaxing agg.</t>
+          <t>Hagfingersvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cuphophyllus virgineus s.lat.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Clavulinopsis helvola</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Pers.) Corner</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2029,10 +2014,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>494170</v>
+        <v>494182</v>
       </c>
       <c r="R14" t="n">
-        <v>6416903</v>
+        <v>6416891</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2090,38 +2075,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129332117</t>
+          <t>https://artportalen.se/Sighting/129332146</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129332123</v>
+        <v>129332155</v>
       </c>
       <c r="B15" t="n">
-        <v>107907</v>
+        <v>88982</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219955</v>
+        <v>3297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slåttergubbe</t>
+          <t>Aprikosfingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Arnica montana</t>
+          <t>Clavulinopsis luteoalba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Rea) Corner</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2131,10 +2116,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>494130</v>
+        <v>494182</v>
       </c>
       <c r="R15" t="n">
-        <v>6416954</v>
+        <v>6416891</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2191,6 +2176,1041 @@
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129332155</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137123856</v>
+      </c>
+      <c r="B16" t="n">
+        <v>89168</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3297</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Aprikosfingersvamp</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Clavulinopsis luteoalba</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Rea) Corner</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>494188</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6416889</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123856</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>119302852</v>
+      </c>
+      <c r="B17" t="n">
+        <v>92632</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>494131</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6417036</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-23</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119302852</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137123858</v>
+      </c>
+      <c r="B18" t="n">
+        <v>89268</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>4374</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Gulvaxing</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hygrocybe chlorophana</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Fr.) Wünsche</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>494174</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6416895</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123858</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129332153</v>
+      </c>
+      <c r="B19" t="n">
+        <v>89083</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>494177</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6416891</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129332153</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137123854</v>
+      </c>
+      <c r="B20" t="n">
+        <v>89270</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>494188</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6416889</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123854</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137123877</v>
+      </c>
+      <c r="B21" t="n">
+        <v>89270</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>4377</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blodvaxing</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Hygrocybe coccinea</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Schaeff.) P.Kumm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>494099</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6416948</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123877</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137123863</v>
+      </c>
+      <c r="B22" t="n">
+        <v>89243</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4385</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Broskvaxing</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Gliophorus laetus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Pers.) Herink</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>494157</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6416933</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123863</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137123876</v>
+      </c>
+      <c r="B23" t="n">
+        <v>89243</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4385</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Broskvaxing</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Gliophorus laetus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Pers.) Herink</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>494099</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6416948</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137123876</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129332117</v>
+      </c>
+      <c r="B24" t="n">
+        <v>89035</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4398</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vitvaxing agg.</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cuphophyllus virgineus s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>494170</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6416903</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129332117</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129332123</v>
+      </c>
+      <c r="B25" t="n">
+        <v>107907</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>219955</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Slåttergubbe</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Arnica montana</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ulstorp, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>494130</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6416954</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jönköping</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Aneby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Marbäck</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-25</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Gabriella Fjordmark Lerne</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129332123</t>
         </is>
@@ -2212,6 +3232,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89291</v>
+        <v>89297</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89298</v>
+        <v>89304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89298</v>
+        <v>89304</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89298</v>
+        <v>89304</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89168</v>
+        <v>89174</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89268</v>
+        <v>89274</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89270</v>
+        <v>89276</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89270</v>
+        <v>89276</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89243</v>
+        <v>89249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89243</v>
+        <v>89249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89297</v>
+        <v>89301</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89304</v>
+        <v>89308</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89304</v>
+        <v>89308</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89304</v>
+        <v>89308</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89174</v>
+        <v>89178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89274</v>
+        <v>89278</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89276</v>
+        <v>89280</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89276</v>
+        <v>89280</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89249</v>
+        <v>89253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89249</v>
+        <v>89253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89301</v>
+        <v>89303</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89308</v>
+        <v>89310</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89308</v>
+        <v>89310</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89308</v>
+        <v>89310</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89178</v>
+        <v>89180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89278</v>
+        <v>89280</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89280</v>
+        <v>89282</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89280</v>
+        <v>89282</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89253</v>
+        <v>89255</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89253</v>
+        <v>89255</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89303</v>
+        <v>89316</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89310</v>
+        <v>89323</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89310</v>
+        <v>89323</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89310</v>
+        <v>89323</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89180</v>
+        <v>89193</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89280</v>
+        <v>89293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89282</v>
+        <v>89295</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89282</v>
+        <v>89295</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89255</v>
+        <v>89268</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89255</v>
+        <v>89268</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89316</v>
+        <v>89318</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89323</v>
+        <v>89325</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89323</v>
+        <v>89325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89323</v>
+        <v>89325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89193</v>
+        <v>89195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89293</v>
+        <v>89295</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89295</v>
+        <v>89297</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89295</v>
+        <v>89297</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89268</v>
+        <v>89270</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89268</v>
+        <v>89270</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89318</v>
+        <v>89321</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89325</v>
+        <v>89328</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89325</v>
+        <v>89328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89325</v>
+        <v>89328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89195</v>
+        <v>89198</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89295</v>
+        <v>89298</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89297</v>
+        <v>89300</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89297</v>
+        <v>89300</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89270</v>
+        <v>89273</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89270</v>
+        <v>89273</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89321</v>
+        <v>89331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89328</v>
+        <v>89338</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89198</v>
+        <v>89208</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89298</v>
+        <v>89308</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89300</v>
+        <v>89310</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89300</v>
+        <v>89310</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89273</v>
+        <v>89283</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89273</v>
+        <v>89283</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89331</v>
+        <v>89332</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89338</v>
+        <v>89339</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89208</v>
+        <v>89209</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89308</v>
+        <v>89309</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89310</v>
+        <v>89311</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89310</v>
+        <v>89311</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89283</v>
+        <v>89284</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89283</v>
+        <v>89284</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89332</v>
+        <v>89335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89339</v>
+        <v>89342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89339</v>
+        <v>89342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89339</v>
+        <v>89342</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89209</v>
+        <v>89212</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89309</v>
+        <v>89312</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89311</v>
+        <v>89314</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89311</v>
+        <v>89314</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89284</v>
+        <v>89287</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89284</v>
+        <v>89287</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89335</v>
+        <v>89340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89342</v>
+        <v>89347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89342</v>
+        <v>89347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89342</v>
+        <v>89347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89212</v>
+        <v>89217</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89312</v>
+        <v>89317</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89314</v>
+        <v>89319</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89314</v>
+        <v>89319</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89287</v>
+        <v>89292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89287</v>
+        <v>89292</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89340</v>
+        <v>89351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89347</v>
+        <v>89358</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89347</v>
+        <v>89358</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89347</v>
+        <v>89358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89217</v>
+        <v>89228</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89317</v>
+        <v>89328</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89319</v>
+        <v>89330</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89319</v>
+        <v>89330</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89292</v>
+        <v>89303</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89292</v>
+        <v>89303</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89351</v>
+        <v>89352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89358</v>
+        <v>89359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89358</v>
+        <v>89359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89358</v>
+        <v>89359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89228</v>
+        <v>89229</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89328</v>
+        <v>89329</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89330</v>
+        <v>89331</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89330</v>
+        <v>89331</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89303</v>
+        <v>89304</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89352</v>
+        <v>89355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89359</v>
+        <v>89362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89359</v>
+        <v>89362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89359</v>
+        <v>89362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89229</v>
+        <v>89232</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89329</v>
+        <v>89332</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89331</v>
+        <v>89334</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89331</v>
+        <v>89334</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89304</v>
+        <v>89307</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89304</v>
+        <v>89307</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 38600-2026 artfynd.xlsx
+++ b/artfynd/A 38600-2026 artfynd.xlsx
@@ -1039,7 +1039,7 @@
         <v>137123861</v>
       </c>
       <c r="B5" t="n">
-        <v>89355</v>
+        <v>89359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>137123857</v>
       </c>
       <c r="B9" t="n">
-        <v>89362</v>
+        <v>89366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>137123859</v>
       </c>
       <c r="B10" t="n">
-        <v>89362</v>
+        <v>89366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137123864</v>
       </c>
       <c r="B11" t="n">
-        <v>89362</v>
+        <v>89366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
         <v>137123856</v>
       </c>
       <c r="B16" t="n">
-        <v>89232</v>
+        <v>89236</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>137123858</v>
       </c>
       <c r="B18" t="n">
-        <v>89332</v>
+        <v>89336</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>137123854</v>
       </c>
       <c r="B20" t="n">
-        <v>89334</v>
+        <v>89338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>137123877</v>
       </c>
       <c r="B21" t="n">
-        <v>89334</v>
+        <v>89338</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>137123863</v>
       </c>
       <c r="B22" t="n">
-        <v>89307</v>
+        <v>89311</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>137123876</v>
       </c>
       <c r="B23" t="n">
-        <v>89307</v>
+        <v>89311</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
